--- a/backend/expense_details.xlsx
+++ b/backend/expense_details.xlsx
@@ -413,13 +413,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>food</v>
+        <v>Food</v>
       </c>
       <c r="B2">
         <v>1000</v>
       </c>
       <c r="C2" s="1">
-        <v>44113.22928240741</v>
+        <v>46166.22928240741</v>
       </c>
     </row>
   </sheetData>
